--- a/artfynd/A 52132-2022 artfynd.xlsx
+++ b/artfynd/A 52132-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52132-2022 artfynd.xlsx
+++ b/artfynd/A 52132-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104778220</v>
+        <v>104778248</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346437.0873189358</v>
+        <v>346636</v>
       </c>
       <c r="R2" t="n">
-        <v>6587643.484573048</v>
+        <v>6587418</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,24 +747,14 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På tallstammar</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104778356</v>
+        <v>104778295</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346597.3486557564</v>
+        <v>346761</v>
       </c>
       <c r="R3" t="n">
-        <v>6587540.61948923</v>
+        <v>6587773</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,24 +854,14 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga i källdråg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104778248</v>
+        <v>104778356</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346635.7879304852</v>
+        <v>346598</v>
       </c>
       <c r="R4" t="n">
-        <v>6587418.232812922</v>
+        <v>6587540</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,24 +961,14 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104778340</v>
+        <v>104778226</v>
       </c>
       <c r="B5" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346631.1643096056</v>
+        <v>346348</v>
       </c>
       <c r="R5" t="n">
-        <v>6587581.049807825</v>
+        <v>6587694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,19 +1067,9 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,37 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104778308</v>
+        <v>104778236</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1199,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346760.5213297271</v>
+        <v>346453</v>
       </c>
       <c r="R6" t="n">
-        <v>6587773.595144214</v>
+        <v>6587350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,19 +1168,9 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,37 +1198,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104778261</v>
+        <v>104778308</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346708.7430858334</v>
+        <v>346761</v>
       </c>
       <c r="R7" t="n">
-        <v>6587617.664139647</v>
+        <v>6587773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,24 +1269,9 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt på flera tallstammar i gammal hällmarksskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,16 +1302,11 @@
         <v>104778214</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1436,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346435.7253240386</v>
+        <v>346436</v>
       </c>
       <c r="R8" t="n">
-        <v>6587685.342734368</v>
+        <v>6587686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,19 +1370,9 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1514,43 +1405,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104778295</v>
+        <v>104778220</v>
       </c>
       <c r="B9" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1558,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>346760.5213297271</v>
+        <v>346437</v>
       </c>
       <c r="R9" t="n">
-        <v>6587773.595144214</v>
+        <v>6587644</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,24 +1476,14 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Granlåga i källdråg</t>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,19 +1511,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104778334</v>
+        <v>104778261</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1679,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346631.1643096056</v>
+        <v>346709</v>
       </c>
       <c r="R10" t="n">
-        <v>6587581.049807825</v>
+        <v>6587618</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,24 +1582,14 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt på flera tallstammar i gammal hällmarksskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,37 +1617,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104778226</v>
+        <v>104778334</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>346347.7517754274</v>
+        <v>346631</v>
       </c>
       <c r="R11" t="n">
-        <v>6587694.528751616</v>
+        <v>6587581</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,19 +1688,14 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,37 +1723,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104778236</v>
+        <v>104778340</v>
       </c>
       <c r="B12" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1916,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>346452.7207030228</v>
+        <v>346631</v>
       </c>
       <c r="R12" t="n">
-        <v>6587349.706843212</v>
+        <v>6587581</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,19 +1794,9 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,12 +1827,7 @@
         <v>104778346</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>346663.6892547873</v>
+        <v>346664</v>
       </c>
       <c r="R13" t="n">
-        <v>6587841.246690952</v>
+        <v>6587841</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,19 +1896,9 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
